--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:51:45+00:00</t>
+    <t>2026-02-03T14:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T14:58:38+00:00</t>
+    <t>2026-02-17T13:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -183,7 +183,7 @@
     <t>LIT</t>
   </si>
   <si>
-    <t>lit</t>
+    <t>Lit</t>
   </si>
   <si>
     <t>PL_TECH</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:17:39+00:00</t>
+    <t>2026-02-17T14:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:34:23+00:00</t>
+    <t>2026-02-22T17:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-location-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:13:24+00:00</t>
+    <t>2026-02-22T17:25:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -558,7 +558,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -570,7 +572,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -582,7 +586,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -594,7 +600,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -606,7 +614,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -618,7 +628,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -630,7 +642,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -642,7 +656,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -654,7 +670,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -666,7 +684,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -678,7 +698,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -690,7 +712,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
